--- a/astro-site/public/dl/ice-cream-shop-checklist-templates/05-ice-cream-shop-cleaning-checklist-maintenance.xlsx
+++ b/astro-site/public/dl/ice-cream-shop-checklist-templates/05-ice-cream-shop-cleaning-checklist-maintenance.xlsx
@@ -931,7 +931,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Take apart and clean the batch freezer parts (dasher, gasket, cylinder)</t>
+          <t>Take apart and clean the batch freezer parts (dasher, scraper blades, door gasket); clean the cylinder in place</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Clean the inside of the storage freezers</t>
+          <t>Clean the inside of the storage freezers (not a task for 14–15-year-olds: FLSA)</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Run the batch freezer empty: check temperature and cycle — log reading: ____ °F</t>
+          <t>Batch freezer check per the manufacturer: scraper blades, dasher and door gasket for wear, and the draw temperature on the day's first batch — never run a freezing cycle with the cylinder empty — log reading: ____ °F</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>If you serve coffee or hot drinks: backflush the group head with detergent, replace the gasket if due and run the dishwasher cleaning cycle (filters and wash arms)</t>
+          <t>If you serve coffee: backflush the group head with detergent and replace the gasket if due. If you have a dishwasher: run its cleaning cycle (filters and wash arms)</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Calculate actual monthly food cost vs target (&lt;28–32%)</t>
+          <t>Calculate actual monthly food cost vs target (28–32% or lower)</t>
         </is>
       </c>
       <c r="C14" s="19" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Allergen check: verify labeling of pre-packed pints (FDA Food Code 3-602.11), traceability and an allergen chart matching the recipes</t>
+          <t>Labeling check: pre-packed pints show name, ingredients, allergens, net weight and shop name and address (FDA Food Code 3-602.11); traceability and an allergen chart matching the recipes</t>
         </is>
       </c>
       <c r="C21" s="19" t="inlineStr">
@@ -2023,7 +2023,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Contracted services — quarterly &amp; semiannual</t>
+          <t>Contracted services — monthly to annual</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Exhaust hood and ducts: if you cook with grease (waffle irons, crepes) under a hood, cleaning by a certified contractor per NFPA 96; a steam-only hood over the pasteurizer, as its manufacturer says</t>
+          <t>Exhaust hood and ducts: if you cook with grease (waffle irons, crepes) under a hood, cleaning by a certified contractor at the NFPA 96 frequency for your cooking volume (low volume, e.g. waffle cones or a seasonal shop: annually); a steam-only hood over the pasteurizer, as its manufacturer says</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -2105,7 +2105,7 @@
       <c r="E7" s="12" t="n"/>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>Semiannual</t>
+          <t>Annual</t>
         </is>
       </c>
       <c r="G7" s="13" t="n"/>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Backflow preventers tested by a certified tester where your water utility requires it (most do, yearly): dipper wells, ice machine and espresso machine all hook up to the water supply</t>
+          <t>Backflow preventers tested by a certified tester where your water utility requires it (most do, yearly): dipper wells, the ice machine and any espresso machine hook up to the water supply</t>
         </is>
       </c>
       <c r="C15" s="19" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Check your health permit is current and posted — and, if you make your own ice cream or pasteurize your own mix, your state frozen dessert / dairy license too</t>
+          <t>Check your health permit is current and posted — and, if you pasteurize your own mix (or your state also licenses batch-freezing or soft serve), your state frozen dessert / dairy license too</t>
         </is>
       </c>
       <c r="C19" s="19" t="inlineStr">
